--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124092489</v>
+        <v>124089781</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,53 +1059,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551676</v>
+        <v>551705</v>
       </c>
       <c r="R5" t="n">
-        <v>6648459</v>
+        <v>6648395</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 200 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,6 +1158,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1171,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124090044</v>
+        <v>124088202</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1206,7 +1212,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1219,14 +1225,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551702</v>
+        <v>551846</v>
       </c>
       <c r="R6" t="n">
-        <v>6648420</v>
+        <v>6648142</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1258,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,7 +1274,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124093144</v>
+        <v>124092489</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,53 +1319,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551646</v>
+        <v>551676</v>
       </c>
       <c r="R7" t="n">
-        <v>6648390</v>
+        <v>6648459</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1393,12 +1404,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,7 +1413,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,7 +1431,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124093197</v>
+        <v>124090044</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1461,7 +1466,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,14 +1479,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551671</v>
+        <v>551702</v>
       </c>
       <c r="R8" t="n">
-        <v>6648402</v>
+        <v>6648420</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1513,7 +1518,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1523,7 +1528,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,7 +1556,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124089781</v>
+        <v>124093197</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1586,12 +1591,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551705</v>
+        <v>551671</v>
       </c>
       <c r="R9" t="n">
-        <v>6648395</v>
+        <v>6648402</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1638,7 +1643,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1648,12 +1653,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 200 ex</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,7 +1681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124088202</v>
+        <v>124093144</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551846</v>
+        <v>551646</v>
       </c>
       <c r="R10" t="n">
-        <v>6648142</v>
+        <v>6648390</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 2 kvm</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124088713</v>
+        <v>124090145</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551771</v>
+        <v>551671</v>
       </c>
       <c r="R11" t="n">
-        <v>6648353</v>
+        <v>6648384</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Myllgrop</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124090145</v>
+        <v>124088713</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551671</v>
+        <v>551771</v>
       </c>
       <c r="R12" t="n">
-        <v>6648384</v>
+        <v>6648353</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Myllgrop</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123928094</v>
+        <v>124087909</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2093,17 +2093,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551631</v>
+        <v>551733</v>
       </c>
       <c r="R13" t="n">
-        <v>6648393</v>
+        <v>6648055</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124087909</v>
+        <v>123928094</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2214,17 +2214,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551733</v>
+        <v>551631</v>
       </c>
       <c r="R14" t="n">
-        <v>6648055</v>
+        <v>6648393</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,22 +2248,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1047,7 +1047,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124089781</v>
+        <v>124090044</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1095,14 +1095,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551705</v>
+        <v>551702</v>
       </c>
       <c r="R5" t="n">
-        <v>6648395</v>
+        <v>6648420</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 200 ex</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,7 +1172,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124088202</v>
+        <v>124093144</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1212,7 +1207,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1229,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551846</v>
+        <v>551646</v>
       </c>
       <c r="R6" t="n">
-        <v>6648142</v>
+        <v>6648390</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1264,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1274,12 +1269,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 2 kvm</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124092489</v>
+        <v>124093197</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1319,53 +1314,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551676</v>
+        <v>551671</v>
       </c>
       <c r="R7" t="n">
-        <v>6648459</v>
+        <v>6648402</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,6 +1408,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1431,7 +1427,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124090044</v>
+        <v>124088202</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1466,7 +1462,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1479,14 +1475,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551702</v>
+        <v>551846</v>
       </c>
       <c r="R8" t="n">
-        <v>6648420</v>
+        <v>6648142</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1518,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1528,7 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,7 +1557,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124093197</v>
+        <v>124089781</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1591,12 +1592,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1608,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551671</v>
+        <v>551705</v>
       </c>
       <c r="R9" t="n">
-        <v>6648402</v>
+        <v>6648395</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1643,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1653,7 +1654,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 200 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124093144</v>
+        <v>124092489</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,53 +1699,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551646</v>
+        <v>551676</v>
       </c>
       <c r="R10" t="n">
-        <v>6648390</v>
+        <v>6648459</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1768,7 +1774,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,12 +1784,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,7 +1793,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124090145</v>
+        <v>123928094</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1851,17 +1851,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551671</v>
+        <v>551631</v>
       </c>
       <c r="R11" t="n">
-        <v>6648384</v>
+        <v>6648393</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,27 +1885,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Myllgrop</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124087909</v>
+        <v>124090145</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551733</v>
+        <v>551671</v>
       </c>
       <c r="R13" t="n">
-        <v>6648055</v>
+        <v>6648384</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Myllgrop</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2174,7 +2174,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123928094</v>
+        <v>124087909</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2214,17 +2214,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551631</v>
+        <v>551733</v>
       </c>
       <c r="R14" t="n">
-        <v>6648393</v>
+        <v>6648055</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,22 +2248,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1040,17 +1040,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Thomas Norström, Lillis Norén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124090044</v>
+        <v>124092489</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,53 +1059,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551702</v>
+        <v>551676</v>
       </c>
       <c r="R5" t="n">
-        <v>6648420</v>
+        <v>6648459</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1153,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1172,7 +1171,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124093144</v>
+        <v>124089781</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1207,12 +1206,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1224,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551646</v>
+        <v>551705</v>
       </c>
       <c r="R6" t="n">
-        <v>6648390</v>
+        <v>6648395</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1259,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Ca 200 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,7 +1301,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124093197</v>
+        <v>124088202</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1337,7 +1336,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1354,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551671</v>
+        <v>551846</v>
       </c>
       <c r="R7" t="n">
-        <v>6648402</v>
+        <v>6648142</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1389,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1398,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,7 +1431,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124088202</v>
+        <v>124093144</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1462,7 +1466,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1479,10 +1483,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551846</v>
+        <v>551646</v>
       </c>
       <c r="R8" t="n">
-        <v>6648142</v>
+        <v>6648390</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1514,7 +1518,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,12 +1528,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 2 kvm</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,7 +1561,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124089781</v>
+        <v>124090044</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1592,12 +1596,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1605,14 +1609,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551705</v>
+        <v>551702</v>
       </c>
       <c r="R9" t="n">
-        <v>6648395</v>
+        <v>6648420</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1644,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1654,12 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 200 ex</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,10 +1686,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124092489</v>
+        <v>124093197</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,53 +1698,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551676</v>
+        <v>551671</v>
       </c>
       <c r="R10" t="n">
-        <v>6648459</v>
+        <v>6648402</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1773,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1783,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,6 +1792,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123928094</v>
+        <v>124090145</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1851,17 +1851,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551631</v>
+        <v>551671</v>
       </c>
       <c r="R11" t="n">
-        <v>6648393</v>
+        <v>6648384</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,27 +1885,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Myllgrop</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124090145</v>
+        <v>123928094</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2093,17 +2093,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551671</v>
+        <v>551631</v>
       </c>
       <c r="R13" t="n">
-        <v>6648384</v>
+        <v>6648393</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,27 +2127,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Myllgrop</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Thomas Norström, Lillis Norén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1040,17 +1040,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Thomas Norström, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124092489</v>
+        <v>124093144</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,53 +1059,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551676</v>
+        <v>551646</v>
       </c>
       <c r="R5" t="n">
-        <v>6648459</v>
+        <v>6648390</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,6 +1158,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1171,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124089781</v>
+        <v>124090044</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1206,12 +1212,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1219,14 +1225,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551705</v>
+        <v>551702</v>
       </c>
       <c r="R6" t="n">
-        <v>6648395</v>
+        <v>6648420</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1258,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1274,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 200 ex</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1302,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124088202</v>
+        <v>124089781</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1336,12 +1337,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1353,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551846</v>
+        <v>551705</v>
       </c>
       <c r="R7" t="n">
-        <v>6648142</v>
+        <v>6648395</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1388,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,12 +1399,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 2 kvm</t>
+          <t>Ca 200 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,7 +1432,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124093144</v>
+        <v>124088202</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1466,7 +1467,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1483,10 +1484,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551646</v>
+        <v>551846</v>
       </c>
       <c r="R8" t="n">
-        <v>6648390</v>
+        <v>6648142</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1518,7 +1519,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1528,12 +1529,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,7 +1562,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124090044</v>
+        <v>124093197</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1596,7 +1597,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1609,14 +1610,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551702</v>
+        <v>551671</v>
       </c>
       <c r="R9" t="n">
-        <v>6648420</v>
+        <v>6648402</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1648,7 +1649,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1658,7 +1659,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124093197</v>
+        <v>124092489</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1698,53 +1699,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551671</v>
+        <v>551676</v>
       </c>
       <c r="R10" t="n">
-        <v>6648402</v>
+        <v>6648459</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1773,7 +1774,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1783,7 +1784,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,7 +1793,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123928094</v>
+        <v>124087909</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2093,17 +2093,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551631</v>
+        <v>551733</v>
       </c>
       <c r="R13" t="n">
-        <v>6648393</v>
+        <v>6648055</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Thomas Norström, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124087909</v>
+        <v>123928094</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2214,17 +2214,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551733</v>
+        <v>551631</v>
       </c>
       <c r="R14" t="n">
-        <v>6648055</v>
+        <v>6648393</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,22 +2248,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1047,7 +1047,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124093144</v>
+        <v>124093197</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551646</v>
+        <v>551671</v>
       </c>
       <c r="R5" t="n">
-        <v>6648390</v>
+        <v>6648402</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124090044</v>
+        <v>124092489</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,53 +1184,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551702</v>
+        <v>551676</v>
       </c>
       <c r="R6" t="n">
-        <v>6648420</v>
+        <v>6648459</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1274,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,7 +1278,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1432,7 +1426,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124088202</v>
+        <v>124090044</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1467,7 +1461,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1480,14 +1474,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551846</v>
+        <v>551702</v>
       </c>
       <c r="R8" t="n">
-        <v>6648142</v>
+        <v>6648420</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1519,7 +1513,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1529,12 +1523,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 2 kvm</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1562,7 +1551,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124093197</v>
+        <v>124088202</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1597,7 +1586,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1614,10 +1603,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551671</v>
+        <v>551846</v>
       </c>
       <c r="R9" t="n">
-        <v>6648402</v>
+        <v>6648142</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1649,7 +1638,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1659,7 +1648,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124092489</v>
+        <v>124093144</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,53 +1693,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551676</v>
+        <v>551646</v>
       </c>
       <c r="R10" t="n">
-        <v>6648459</v>
+        <v>6648390</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1778,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1793,6 +1792,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124090145</v>
+        <v>124088713</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551671</v>
+        <v>551771</v>
       </c>
       <c r="R11" t="n">
-        <v>6648384</v>
+        <v>6648353</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Myllgrop</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1932,7 +1932,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124088713</v>
+        <v>124090145</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551771</v>
+        <v>551671</v>
       </c>
       <c r="R12" t="n">
-        <v>6648353</v>
+        <v>6648384</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Myllgrop</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124087909</v>
+        <v>123928094</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2093,17 +2093,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551733</v>
+        <v>551631</v>
       </c>
       <c r="R13" t="n">
-        <v>6648055</v>
+        <v>6648393</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123928094</v>
+        <v>124087909</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2214,17 +2214,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551631</v>
+        <v>551733</v>
       </c>
       <c r="R14" t="n">
-        <v>6648393</v>
+        <v>6648055</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,22 +2248,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1047,7 +1047,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124093197</v>
+        <v>124093144</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551671</v>
+        <v>551646</v>
       </c>
       <c r="R5" t="n">
-        <v>6648402</v>
+        <v>6648390</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124092489</v>
+        <v>124089781</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,53 +1189,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551676</v>
+        <v>551705</v>
       </c>
       <c r="R6" t="n">
-        <v>6648459</v>
+        <v>6648395</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1274,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 200 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,6 +1288,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1296,7 +1307,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124089781</v>
+        <v>124090044</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1331,12 +1342,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1344,14 +1355,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551705</v>
+        <v>551702</v>
       </c>
       <c r="R7" t="n">
-        <v>6648395</v>
+        <v>6648420</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1383,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1393,12 +1404,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 200 ex</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,7 +1432,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124090044</v>
+        <v>124093197</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1461,7 +1467,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,14 +1480,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551702</v>
+        <v>551671</v>
       </c>
       <c r="R8" t="n">
-        <v>6648420</v>
+        <v>6648402</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1513,7 +1519,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1523,7 +1529,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1551,10 +1557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124088202</v>
+        <v>124092489</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,53 +1569,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551846</v>
+        <v>551676</v>
       </c>
       <c r="R9" t="n">
-        <v>6648142</v>
+        <v>6648459</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1638,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1648,12 +1654,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ca 2 kvm</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1662,7 +1663,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1681,7 +1681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124093144</v>
+        <v>124088202</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551646</v>
+        <v>551846</v>
       </c>
       <c r="R10" t="n">
-        <v>6648390</v>
+        <v>6648142</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124088713</v>
+        <v>123928094</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1851,17 +1851,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551771</v>
+        <v>551631</v>
       </c>
       <c r="R11" t="n">
-        <v>6648353</v>
+        <v>6648393</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,22 +1885,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123928094</v>
+        <v>124087909</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2093,17 +2093,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551631</v>
+        <v>551733</v>
       </c>
       <c r="R13" t="n">
-        <v>6648393</v>
+        <v>6648055</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +2127,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2167,14 +2167,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124087909</v>
+        <v>124088713</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551733</v>
+        <v>551771</v>
       </c>
       <c r="R14" t="n">
-        <v>6648055</v>
+        <v>6648353</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1047,7 +1047,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124093144</v>
+        <v>124088202</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551646</v>
+        <v>551846</v>
       </c>
       <c r="R5" t="n">
-        <v>6648390</v>
+        <v>6648142</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Ca 2 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124089781</v>
+        <v>124093144</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551705</v>
+        <v>551646</v>
       </c>
       <c r="R6" t="n">
-        <v>6648395</v>
+        <v>6648390</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 200 ex</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124090044</v>
+        <v>124089781</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1355,14 +1355,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551702</v>
+        <v>551705</v>
       </c>
       <c r="R7" t="n">
-        <v>6648420</v>
+        <v>6648395</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1404,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 200 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1681,7 +1686,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124088202</v>
+        <v>124090044</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1716,7 +1721,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1729,14 +1734,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551846</v>
+        <v>551702</v>
       </c>
       <c r="R10" t="n">
-        <v>6648142</v>
+        <v>6648420</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1768,7 +1773,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,12 +1783,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 2 kvm</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123928094</v>
+        <v>124087909</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1851,17 +1851,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551631</v>
+        <v>551733</v>
       </c>
       <c r="R11" t="n">
-        <v>6648393</v>
+        <v>6648055</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,22 +1885,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1925,14 +1925,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124090145</v>
+        <v>123928094</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1972,17 +1972,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551671</v>
+        <v>551631</v>
       </c>
       <c r="R12" t="n">
-        <v>6648384</v>
+        <v>6648393</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2006,27 +2006,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Myllgrop</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,14 +2046,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124087909</v>
+        <v>124088713</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551733</v>
+        <v>551771</v>
       </c>
       <c r="R13" t="n">
-        <v>6648055</v>
+        <v>6648353</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2174,7 +2174,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124088713</v>
+        <v>124090145</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551771</v>
+        <v>551671</v>
       </c>
       <c r="R14" t="n">
-        <v>6648353</v>
+        <v>6648384</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Myllgrop</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -1811,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124087909</v>
+        <v>124090145</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551733</v>
+        <v>551671</v>
       </c>
       <c r="R11" t="n">
-        <v>6648055</v>
+        <v>6648384</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Myllgrop</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2053,7 +2053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124088713</v>
+        <v>124087909</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551771</v>
+        <v>551733</v>
       </c>
       <c r="R13" t="n">
-        <v>6648353</v>
+        <v>6648055</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2174,7 +2174,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124090145</v>
+        <v>124088713</v>
       </c>
       <c r="B14" t="n">
         <v>56722</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551671</v>
+        <v>551771</v>
       </c>
       <c r="R14" t="n">
-        <v>6648384</v>
+        <v>6648353</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Myllgrop</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73893709</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551765.7509025953</v>
+        <v>551766</v>
       </c>
       <c r="R2" t="n">
-        <v>6648262.203949692</v>
+        <v>6648262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2018-11-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73893710</v>
+        <v>73893711</v>
       </c>
       <c r="B3" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551680.1383328043</v>
+        <v>551685</v>
       </c>
       <c r="R3" t="n">
-        <v>6648465.809065542</v>
+        <v>6648477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +858,9 @@
           <t>2018-11-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-11-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,65 +887,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123925925</v>
+        <v>73893710</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Ombenning, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551676</v>
+        <v>551680</v>
       </c>
       <c r="R4" t="n">
-        <v>6648459</v>
+        <v>6648466</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,27 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 20 ex</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,84 +975,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124088202</v>
+        <v>73893694</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Ombenning, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551846</v>
+        <v>551940</v>
       </c>
       <c r="R5" t="n">
-        <v>6648142</v>
+        <v>6648431</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,32 +1062,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Fagersta</t>
+          <t>Västervåla</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 2 kvm</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,84 +1081,75 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124093144</v>
+        <v>73893705</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Ombenning, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551646</v>
+        <v>551607</v>
       </c>
       <c r="R6" t="n">
-        <v>6648390</v>
+        <v>6648098</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,27 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,84 +1187,75 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124089781</v>
+        <v>73893708</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Ombenning, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551705</v>
+        <v>551711</v>
       </c>
       <c r="R7" t="n">
-        <v>6648395</v>
+        <v>6648266</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,27 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 200 ex</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,84 +1293,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124093197</v>
+        <v>123928094</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551671</v>
+        <v>551631</v>
       </c>
       <c r="R8" t="n">
-        <v>6648402</v>
+        <v>6648393</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1519,22 +1380,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,7 +1409,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1555,67 +1420,59 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124092489</v>
+        <v>124087909</v>
       </c>
       <c r="B9" t="n">
-        <v>58050</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551676</v>
+        <v>551733</v>
       </c>
       <c r="R9" t="n">
-        <v>6648459</v>
+        <v>6648055</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,7 +1501,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1654,7 +1511,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,62 +1543,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124090044</v>
+        <v>124088713</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fågelmossen, Fågelmossen, Vstm</t>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551702</v>
+        <v>551771</v>
       </c>
       <c r="R10" t="n">
-        <v>6648420</v>
+        <v>6648353</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1768,7 +1617,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1778,7 +1627,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,7 +1641,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1809,12 +1662,7 @@
         <v>124090145</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,54 +1775,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123928094</v>
+        <v>124092489</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551631</v>
+        <v>551676</v>
       </c>
       <c r="R12" t="n">
-        <v>6648393</v>
+        <v>6648459</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2001,27 +1852,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,64 +1887,63 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124087909</v>
+        <v>123695287</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>206046</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Västanfors sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551733</v>
+        <v>551609</v>
       </c>
       <c r="R13" t="n">
-        <v>6648055</v>
+        <v>6648382</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2122,27 +1967,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:52</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,69 +1987,72 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas</t>
+          <t>Pentti Korhonen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Seppo Ormiskangas, Lillis Norén</t>
+          <t>Pentti Korhonen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124088713</v>
+        <v>123925925</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+          <t>Fågelmossen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551771</v>
+        <v>551676</v>
       </c>
       <c r="R14" t="n">
-        <v>6648353</v>
+        <v>6648459</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2243,27 +2076,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Ca 20 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2272,6 +2105,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2283,10 +2117,625 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>Seppo Ormiskangas, Lillis Norén, Thomas Norström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124088202</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>551846</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6648142</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 2 kvm</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Seppo Ormiskangas, Lillis Norén</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124089781</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>551705</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6648395</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 200 ex</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124090044</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fågelmossen, Fågelmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>551702</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6648420</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124093144</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>551646</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6648390</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124093197</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fågelmossberget, Fågelmossberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>551671</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6648402</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fagersta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Seppo Ormiskangas, Lillis Norén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12909-2025 artfynd.xlsx
+++ b/artfynd/A 12909-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73893709</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73893711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73893710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73893694</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73893705</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73893708</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123928094</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124088713</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124090145</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124092489</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123695287</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2121,6 +2186,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123925925</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2246,6 +2316,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124088202</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2371,6 +2446,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124089781</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2491,6 +2571,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124090044</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2616,6 +2701,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124093144</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2736,8 +2826,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124093197</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>